--- a/Project Data/BOP/Variables.xlsx
+++ b/Project Data/BOP/Variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10922"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellieknott/R Projects/Moldova General/Project Data/BOP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A5E815D-816E-5D4B-B213-E94108956BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1C10D8-02EC-2B48-AB79-0482E4776EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15400" yWindow="1140" windowWidth="13320" windowHeight="16680" xr2:uid="{850DF900-EBB6-4846-A30C-ED9308FDF341}"/>
+    <workbookView xWindow="48420" yWindow="3500" windowWidth="18340" windowHeight="18740" xr2:uid="{850DF900-EBB6-4846-A30C-ED9308FDF341}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="118">
   <si>
     <t>Sandu</t>
   </si>
@@ -342,13 +342,64 @@
   </si>
   <si>
     <t>D16_01</t>
+  </si>
+  <si>
+    <t>problems (1)</t>
+  </si>
+  <si>
+    <t>problems (2)</t>
+  </si>
+  <si>
+    <t>problems (3)</t>
+  </si>
+  <si>
+    <t>D6_2</t>
+  </si>
+  <si>
+    <t>D6_3</t>
+  </si>
+  <si>
+    <t>A_7_1</t>
+  </si>
+  <si>
+    <t>A_7_2</t>
+  </si>
+  <si>
+    <t>A_7_3</t>
+  </si>
+  <si>
+    <t>D17_1</t>
+  </si>
+  <si>
+    <t>D17_2</t>
+  </si>
+  <si>
+    <t>D17_3</t>
+  </si>
+  <si>
+    <t>B6_1</t>
+  </si>
+  <si>
+    <t>B6_2</t>
+  </si>
+  <si>
+    <t>B6_3</t>
+  </si>
+  <si>
+    <t>B6_01</t>
+  </si>
+  <si>
+    <t>B6_02</t>
+  </si>
+  <si>
+    <t>B6_03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -362,6 +413,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -730,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7AEC77-C7DE-E34A-A832-7970743282A5}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -1187,7 +1244,95 @@
         <v>87</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" t="s">
+        <v>116</v>
+      </c>
+      <c r="L17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" t="s">
+        <v>114</v>
+      </c>
+      <c r="K18" t="s">
+        <v>117</v>
+      </c>
+      <c r="L18" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>